--- a/customer-delivery/07 - Marketing/08 - 60-Day Marketing Content Calendar.xlsx
+++ b/customer-delivery/07 - Marketing/08 - 60-Day Marketing Content Calendar.xlsx
@@ -283,6 +283,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -761,7 +764,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Is it 'too early' to start looking into home care? Here's the honest answer: most families wait until a crisis — a fall, a hospital stay — before they even start researching. The families who feel most in control are the ones who start the conversation 6–12 months before they think they'll need it. Waiting for the emergency means less time to find the right fit.</t>
+          <t>Is it 'too early' to start looking into home care? Planning before a crisis can give families more time to compare options, ask questions, and decide what kind of support fits. If you think care may be needed in the coming months, starting the conversation now can reduce last-minute pressure later.</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -1241,7 +1244,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The home care industry keeps growing as more families choose to age at home instead of in a facility — and we understand why. There's no substitute for staying in a familiar space, surrounded by memories, with the right support in place. That's what we're here to provide.</t>
+          <t>Many families explore support at home because remaining in familiar surroundings matters to them. Home care can be one option when a person needs non-medical assistance, companionship, or help with daily routines. The right setting depends on the person's needs, preferences, safety, and available support.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1281,7 +1284,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Memory care at home is possible for many families in earlier stages of dementia or Alzheimer's. Consistent routines, familiar surroundings, and one-on-one attention can actually reduce confusion and agitation compared to an unfamiliar facility environment. It's not right for every stage — but it's worth discussing with your care team.</t>
+          <t>For some people living with dementia, familiar surroundings and consistent routines may be helpful. Home-based support is not appropriate for every person or every stage, so families should discuss changing needs and safety concerns with the person's care team and qualified professionals.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1721,7 +1724,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Hospital readmissions often happen because of small things at home that get missed — a missed follow-up appointment, a medication mix-up, a fall during recovery. A little extra support during the first few weeks home can make a real difference in avoiding a return trip to the hospital.</t>
+          <t>The transition home after a hospital stay can involve many moving parts, such as follow-up appointments, mobility needs, meals, and medication routines. Non-medical home care may help with permitted support tasks during recovery, while medical questions and medication management should stay with qualified clinicians.</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -2001,7 +2004,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Nutrition often slips first when an aging parent starts to struggle — skipped meals, spoiled food, or the same simple snack every day. A caregiver who preps real meals and pays attention to appetite changes can catch health issues early, not just after a hospital visit.</t>
+          <t>Changes in eating habits, meal preparation, or appetite can be useful observations to share with the client, family, or care team when appropriate. A non-medical caregiver can assist with meal preparation and document observations within the agency's permitted scope; caregivers should not diagnose health conditions.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2201,7 +2204,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>What's a myth about home care you believed before you actually looked into it? A lot of families assume it means giving up independence — usually it's the opposite. Curious what you've heard.</t>
+          <t>What's a myth about home care you believed before you looked into it? Some people assume accepting help automatically means giving up independence. In practice, the right support plan is individualized and may help a person continue preferred routines safely. What questions did you have at the beginning?</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2361,7 +2364,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>A short hospital stay can lead to a much longer recovery if the right support isn't in place at home. Transitional care after surgery or illness — medication reminders, mobility help, and a familiar face — often makes the difference between a smooth recovery and a setback.</t>
+          <t>Coming home after surgery or illness can require extra coordination. Depending on the person's needs and the agency's permitted scope, non-medical transitional support may include meal preparation, transportation, mobility assistance, companionship, and medication reminders. Clinical care and medical decisions remain with licensed professionals.</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2441,7 +2444,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Grief and caregiving often overlap in ways people don't talk about enough — grieving the parent someone used to be, even while they're still here. If you're feeling that, you're not doing anything wrong. It's a real and common part of this journey.</t>
+          <t>Caregiving can bring many emotions, including sadness, stress, and a sense of loss as a loved one's needs change. Experiences differ from family to family. If caregiving stress or grief feels overwhelming, consider reaching out to a qualified counselor, support group, faith leader, or healthcare professional.</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2641,7 +2644,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Sundowning — increased confusion or agitation in the evening — is common in dementia care and can catch families off guard. Consistent evening routines, good lighting, and calm reassurance from a familiar caregiver can ease the transition.</t>
+          <t>Some people living with dementia experience increased confusion or agitation later in the day, often described as sundowning. Families sometimes find that predictable routines, appropriate lighting, and a calm environment are helpful, but needs vary. Discuss significant behavior changes or safety concerns with the person's care team.</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2761,7 +2764,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>The difference between 'independent' and 'isolated' is often just regular company. A parent living alone can be perfectly capable and still benefit enormously from a friendly, consistent visit a few times a week.</t>
+          <t>Living independently does not always mean a person wants to spend most of the day alone. For some older adults, regular companionship can add conversation, activities, and practical support while respecting independence and personal preferences.</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
